--- a/7711 Bible memorization/Scripture design v1.2.xlsx
+++ b/7711 Bible memorization/Scripture design v1.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Documents\Study\memory\repo\7711 Bible memorization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7031D08-69F4-4091-A369-FFE219862F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53A9BF8-00C3-4D84-BD57-F5B365B29989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Books" sheetId="2" r:id="rId1"/>
@@ -2205,9 +2205,6 @@
     <t>The whale is scared off by a tiny chihuahua stuffed toy on leash purchased by a fancy woman tourist.</t>
   </si>
   <si>
-    <t>A high diver lauches off of Noah's ark doing multiple twists and turns to a pool below.</t>
-  </si>
-  <si>
     <t>An official shoots ammo to signal start of the freestyle event where the diver has gone.</t>
   </si>
   <si>
@@ -4660,6 +4657,9 @@
   </si>
   <si>
     <t>fighting weapons</t>
+  </si>
+  <si>
+    <t>A high diver bounces on his knees out to the end of the diving board and then does multiple twists and turns to a pool below.</t>
   </si>
 </sst>
 </file>
@@ -5660,25 +5660,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="D1" t="s">
         <v>845</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>846</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>847</v>
       </c>
-      <c r="F1" t="s">
-        <v>848</v>
-      </c>
       <c r="G1" s="18" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
@@ -5686,20 +5686,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>849</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>850</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>851</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="20" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
@@ -5707,20 +5707,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>852</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>853</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="20" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
@@ -5728,20 +5728,20 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>854</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>855</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="20" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
@@ -5749,20 +5749,20 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>856</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>857</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>858</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="20" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -5770,20 +5770,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>137</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>859</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>860</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="20" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -5791,20 +5791,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>139</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>861</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>862</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -5812,20 +5812,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>180</v>
       </c>
       <c r="D8" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>863</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>864</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -5833,20 +5833,20 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>864</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>865</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>866</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -5854,20 +5854,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>867</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>868</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>869</v>
       </c>
       <c r="F10" s="9"/>
       <c r="G10" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
@@ -5875,20 +5875,20 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>870</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>871</v>
       </c>
       <c r="F11" s="9"/>
       <c r="G11" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -5896,20 +5896,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>236</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>872</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>873</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -5917,20 +5917,20 @@
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>189</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>873</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>874</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>875</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -5938,20 +5938,20 @@
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>153</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>876</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>877</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -5959,20 +5959,20 @@
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>242</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>878</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>879</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -5980,20 +5980,20 @@
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>110</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>879</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>880</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>881</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -6001,20 +6001,20 @@
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>881</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>882</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>883</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>884</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -6022,20 +6022,20 @@
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>885</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="E18" s="9" t="s">
         <v>886</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>887</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -6043,20 +6043,20 @@
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="E19" s="9" t="s">
         <v>889</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>890</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="19" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -6064,20 +6064,20 @@
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>891</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="E20" s="9" t="s">
         <v>892</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>893</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="19" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -6085,20 +6085,20 @@
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>894</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="E21" s="9" t="s">
         <v>895</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>896</v>
       </c>
       <c r="F21" s="9"/>
       <c r="G21" s="19" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -6106,20 +6106,20 @@
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>897</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>898</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="19" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -6127,20 +6127,20 @@
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C23" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>899</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>900</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>901</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="19" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -6148,20 +6148,20 @@
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C24" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>902</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="E24" s="9" t="s">
         <v>903</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>904</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="19" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -6169,22 +6169,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C25" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>905</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>1537</v>
-      </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>906</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>907</v>
-      </c>
       <c r="G25" s="19" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -6192,22 +6192,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>213</v>
       </c>
       <c r="D26" s="9" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>907</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>1538</v>
       </c>
-      <c r="E26" s="9" t="s">
-        <v>908</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>1539</v>
-      </c>
       <c r="G26" s="19" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
@@ -6215,20 +6215,20 @@
         <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C27" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>909</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="E27" s="9" t="s">
         <v>910</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>911</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="19" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -6236,20 +6236,20 @@
         <v>27</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C28" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>912</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="E28" s="9" t="s">
         <v>913</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>914</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="19" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
@@ -6257,22 +6257,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>55</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>915</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>916</v>
-      </c>
       <c r="F29" s="9" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -6280,20 +6280,20 @@
         <v>29</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C30" s="9" t="s">
+        <v>916</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>917</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="E30" s="9" t="s">
         <v>918</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>919</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -6301,20 +6301,20 @@
         <v>30</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>920</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="E31" s="9" t="s">
         <v>921</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>922</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -6322,20 +6322,20 @@
         <v>31</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C32" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>923</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="E32" s="9" t="s">
         <v>924</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>925</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
@@ -6343,20 +6343,20 @@
         <v>32</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>925</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>926</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>927</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>928</v>
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
@@ -6364,20 +6364,20 @@
         <v>33</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>928</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>929</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="E34" s="9" t="s">
         <v>930</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>931</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
@@ -6385,22 +6385,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>931</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>932</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="E35" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="F35" s="9" t="s">
         <v>934</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>935</v>
-      </c>
       <c r="G35" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
@@ -6408,22 +6408,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C36" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>936</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>937</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="F36" s="9" t="s">
         <v>938</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>939</v>
-      </c>
       <c r="G36" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -6431,20 +6431,20 @@
         <v>36</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C37" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>940</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="E37" s="9" t="s">
         <v>941</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>942</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -6452,20 +6452,20 @@
         <v>37</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C38" s="9" t="s">
+        <v>942</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>943</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="E38" s="9" t="s">
         <v>944</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>945</v>
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -6473,22 +6473,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C39" s="9" t="s">
+        <v>945</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>946</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="E39" s="9" t="s">
         <v>947</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="F39" s="9" t="s">
         <v>948</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>949</v>
-      </c>
       <c r="G39" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -6496,20 +6496,20 @@
         <v>39</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C40" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>950</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="E40" s="9" t="s">
         <v>951</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>952</v>
       </c>
       <c r="F40" s="9"/>
       <c r="G40" s="19" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -6517,22 +6517,22 @@
         <v>1</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C41" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>953</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="E41" s="9" t="s">
         <v>954</v>
       </c>
-      <c r="E41" s="9" t="s">
-        <v>955</v>
-      </c>
       <c r="F41" s="9" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -6540,22 +6540,22 @@
         <v>2</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C42" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>956</v>
       </c>
-      <c r="D42" s="9" t="s">
-        <v>957</v>
-      </c>
       <c r="E42" s="9" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G42" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -6563,22 +6563,22 @@
         <v>3</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>469</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G43" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -6586,22 +6586,22 @@
         <v>4</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>387</v>
       </c>
       <c r="D44" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="E44" s="9" t="s">
         <v>959</v>
       </c>
-      <c r="E44" s="9" t="s">
-        <v>960</v>
-      </c>
       <c r="F44" s="9" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G44" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -6609,22 +6609,22 @@
         <v>5</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>361</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>485</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -6632,22 +6632,22 @@
         <v>6</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C46" s="9" t="s">
+        <v>961</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>962</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>963</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>486</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
@@ -6655,22 +6655,22 @@
         <v>7</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>180</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>487</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
@@ -6678,22 +6678,22 @@
         <v>8</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>15</v>
       </c>
       <c r="D48" s="9" t="s">
+        <v>964</v>
+      </c>
+      <c r="E48" s="9" t="s">
         <v>965</v>
       </c>
-      <c r="E48" s="9" t="s">
-        <v>966</v>
-      </c>
       <c r="F48" s="9" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
@@ -6701,22 +6701,22 @@
         <v>9</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C49" s="9" t="s">
+        <v>966</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>967</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="E49" s="9" t="s">
         <v>968</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="F49" s="9" t="s">
         <v>969</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>970</v>
-      </c>
       <c r="G49" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
@@ -6724,22 +6724,22 @@
         <v>10</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C50" s="9" t="s">
+        <v>970</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>971</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>972</v>
-      </c>
       <c r="E50" s="13" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
@@ -6747,22 +6747,22 @@
         <v>11</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C51" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>973</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="E51" s="9" t="s">
         <v>974</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="F51" s="9" t="s">
         <v>975</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>976</v>
-      </c>
       <c r="G51" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
@@ -6770,22 +6770,22 @@
         <v>12</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>189</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>490</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G52" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
@@ -6793,20 +6793,20 @@
         <v>13</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>240</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>491</v>
       </c>
       <c r="F53" s="9"/>
       <c r="G53" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -6814,20 +6814,20 @@
         <v>14</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C54" s="9" t="s">
+        <v>979</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>980</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="E54" s="9" t="s">
         <v>981</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>982</v>
       </c>
       <c r="F54" s="9"/>
       <c r="G54" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -6835,20 +6835,20 @@
         <v>15</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>110</v>
       </c>
       <c r="D55" s="9" t="s">
+        <v>982</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>983</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>984</v>
       </c>
       <c r="F55" s="9"/>
       <c r="G55" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
@@ -6856,20 +6856,20 @@
         <v>16</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>496</v>
       </c>
       <c r="F56" s="9"/>
       <c r="G56" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
@@ -6877,20 +6877,20 @@
         <v>17</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C57" s="9" t="s">
+        <v>985</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>986</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>987</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>498</v>
       </c>
       <c r="F57" s="9"/>
       <c r="G57" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
@@ -6898,20 +6898,20 @@
         <v>18</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C58" s="9" t="s">
+        <v>987</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>988</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>989</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>500</v>
       </c>
       <c r="F58" s="9"/>
       <c r="G58" s="19" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
@@ -6919,20 +6919,20 @@
         <v>19</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C59" s="9" t="s">
+        <v>989</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>990</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>991</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>502</v>
       </c>
       <c r="F59" s="9"/>
       <c r="G59" s="19" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
@@ -6940,22 +6940,22 @@
         <v>20</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>507</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
@@ -6963,20 +6963,20 @@
         <v>21</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D61" s="9" t="s">
+        <v>993</v>
+      </c>
+      <c r="E61" s="9" t="s">
         <v>994</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>995</v>
       </c>
       <c r="F61" s="9"/>
       <c r="G61" s="19" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
@@ -6984,20 +6984,20 @@
         <v>22</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>437</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>515</v>
       </c>
       <c r="F62" s="9"/>
       <c r="G62" s="19" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
@@ -7005,22 +7005,22 @@
         <v>23</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D63" s="9" t="s">
+        <v>996</v>
+      </c>
+      <c r="E63" s="9" t="s">
         <v>997</v>
       </c>
-      <c r="E63" s="9" t="s">
+      <c r="F63" s="9" t="s">
         <v>998</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>999</v>
-      </c>
       <c r="G63" s="19" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
@@ -7028,20 +7028,20 @@
         <v>24</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C64" s="9" t="s">
+        <v>999</v>
+      </c>
+      <c r="D64" s="9" t="s">
         <v>1000</v>
       </c>
-      <c r="D64" s="9" t="s">
-        <v>1001</v>
-      </c>
       <c r="E64" s="9" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F64" s="9"/>
       <c r="G64" s="19" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
@@ -7049,20 +7049,20 @@
         <v>25</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>213</v>
       </c>
       <c r="D65" s="9" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>1002</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>1003</v>
       </c>
       <c r="F65" s="9"/>
       <c r="G65" s="19" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
@@ -7070,20 +7070,20 @@
         <v>26</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C66" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>1004</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="E66" s="9" t="s">
         <v>1005</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>1006</v>
       </c>
       <c r="F66" s="9"/>
       <c r="G66" s="19" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
@@ -7091,22 +7091,22 @@
         <v>27</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C67" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D67" s="9" t="s">
         <v>1007</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="E67" s="9" t="s">
         <v>1008</v>
       </c>
-      <c r="E67" s="9" t="s">
-        <v>1009</v>
-      </c>
       <c r="F67" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -7137,7 +7137,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>440</v>
@@ -7146,13 +7146,13 @@
         <v>438</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -7166,7 +7166,7 @@
         <v>439</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -7186,7 +7186,7 @@
         <v>439</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>3</v>
@@ -7206,7 +7206,7 @@
         <v>439</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>5</v>
@@ -7226,7 +7226,7 @@
         <v>439</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>7</v>
@@ -7246,7 +7246,7 @@
         <v>439</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>9</v>
@@ -7266,7 +7266,7 @@
         <v>439</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>11</v>
@@ -7286,7 +7286,7 @@
         <v>439</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>13</v>
@@ -7306,7 +7306,7 @@
         <v>439</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>15</v>
@@ -7326,7 +7326,7 @@
         <v>439</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>17</v>
@@ -9649,7 +9649,7 @@
         <v>452</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F126" s="13" t="s">
         <v>582</v>
@@ -9712,7 +9712,7 @@
         <v>236</v>
       </c>
       <c r="F129" s="13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -9732,7 +9732,7 @@
         <v>238</v>
       </c>
       <c r="F130" s="13" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -9752,7 +9752,7 @@
         <v>240</v>
       </c>
       <c r="F131" s="13" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -9772,7 +9772,7 @@
         <v>242</v>
       </c>
       <c r="F132" s="13" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -9972,7 +9972,7 @@
         <v>260</v>
       </c>
       <c r="F142" s="13" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.45">
@@ -10112,7 +10112,7 @@
         <v>110</v>
       </c>
       <c r="F149" s="13" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10429,7 +10429,7 @@
         <v>462</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F165" s="13" t="s">
         <v>710</v>
@@ -10523,7 +10523,7 @@
         <v>10</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D170" s="13" t="s">
         <v>462</v>
@@ -10543,7 +10543,7 @@
         <v>10</v>
       </c>
       <c r="C171" s="13" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D171" s="13" t="s">
         <v>462</v>
@@ -10563,7 +10563,7 @@
         <v>10</v>
       </c>
       <c r="C172" s="13" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D172" s="13" t="s">
         <v>462</v>
@@ -10583,7 +10583,7 @@
         <v>10</v>
       </c>
       <c r="C173" s="13" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D173" s="13" t="s">
         <v>462</v>
@@ -10603,7 +10603,7 @@
         <v>10</v>
       </c>
       <c r="C174" s="13" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D174" s="13" t="s">
         <v>462</v>
@@ -10623,7 +10623,7 @@
         <v>10</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D175" s="13" t="s">
         <v>462</v>
@@ -10652,7 +10652,7 @@
         <v>1</v>
       </c>
       <c r="F176" s="13" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10669,10 +10669,10 @@
         <v>462</v>
       </c>
       <c r="E177" s="13" t="s">
-        <v>249</v>
+        <v>3</v>
       </c>
       <c r="F177" s="13" t="s">
-        <v>722</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10692,7 +10692,7 @@
         <v>251</v>
       </c>
       <c r="F178" s="13" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10712,7 +10712,7 @@
         <v>301</v>
       </c>
       <c r="F179" s="13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10732,7 +10732,7 @@
         <v>1</v>
       </c>
       <c r="F180" s="13" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10752,7 +10752,7 @@
         <v>323</v>
       </c>
       <c r="F181" s="13" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10772,7 +10772,7 @@
         <v>325</v>
       </c>
       <c r="F182" s="13" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.45">
@@ -10792,7 +10792,7 @@
         <v>135</v>
       </c>
       <c r="F183" s="13" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10812,7 +10812,7 @@
         <v>1</v>
       </c>
       <c r="F184" s="13" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.45">
@@ -10832,7 +10832,7 @@
         <v>171</v>
       </c>
       <c r="F185" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.45">
@@ -10852,7 +10852,7 @@
         <v>330</v>
       </c>
       <c r="F186" s="13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.45">
@@ -10872,7 +10872,7 @@
         <v>332</v>
       </c>
       <c r="F187" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10892,7 +10892,7 @@
         <v>334</v>
       </c>
       <c r="F188" s="13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.45">
@@ -10932,7 +10932,7 @@
         <v>337</v>
       </c>
       <c r="F190" s="13" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10952,7 +10952,7 @@
         <v>330</v>
       </c>
       <c r="F191" s="13" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10972,7 +10972,7 @@
         <v>1</v>
       </c>
       <c r="F192" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -10992,7 +10992,7 @@
         <v>171</v>
       </c>
       <c r="F193" s="13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11012,7 +11012,7 @@
         <v>133</v>
       </c>
       <c r="F194" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11032,7 +11032,7 @@
         <v>343</v>
       </c>
       <c r="F195" s="13" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11052,7 +11052,7 @@
         <v>280</v>
       </c>
       <c r="F196" s="13" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11092,7 +11092,7 @@
         <v>1</v>
       </c>
       <c r="F198" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11132,7 +11132,7 @@
         <v>349</v>
       </c>
       <c r="F200" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11152,7 +11152,7 @@
         <v>312</v>
       </c>
       <c r="F201" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.45">
@@ -11172,7 +11172,7 @@
         <v>1</v>
       </c>
       <c r="F202" s="13" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.45">
@@ -11192,7 +11192,7 @@
         <v>3</v>
       </c>
       <c r="F203" s="13" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11252,7 +11252,7 @@
         <v>1</v>
       </c>
       <c r="F206" s="13" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11272,7 +11272,7 @@
         <v>249</v>
       </c>
       <c r="F207" s="13" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11292,7 +11292,7 @@
         <v>358</v>
       </c>
       <c r="F208" s="13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11312,7 +11312,7 @@
         <v>135</v>
       </c>
       <c r="F209" s="13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11332,7 +11332,7 @@
         <v>361</v>
       </c>
       <c r="F210" s="13" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11352,7 +11352,7 @@
         <v>139</v>
       </c>
       <c r="F211" s="13" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11372,7 +11372,7 @@
         <v>364</v>
       </c>
       <c r="F212" s="13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11392,7 +11392,7 @@
         <v>366</v>
       </c>
       <c r="F213" s="13" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11412,7 +11412,7 @@
         <v>368</v>
       </c>
       <c r="F214" s="13" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11452,7 +11452,7 @@
         <v>236</v>
       </c>
       <c r="F216" s="13" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11472,7 +11472,7 @@
         <v>373</v>
       </c>
       <c r="F217" s="13" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11492,7 +11492,7 @@
         <v>107</v>
       </c>
       <c r="F218" s="13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11532,7 +11532,7 @@
         <v>3</v>
       </c>
       <c r="F220" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11552,7 +11552,7 @@
         <v>251</v>
       </c>
       <c r="F221" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="222" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11572,7 +11572,7 @@
         <v>379</v>
       </c>
       <c r="F222" s="13" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11592,7 +11592,7 @@
         <v>381</v>
       </c>
       <c r="F223" s="13" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11612,7 +11612,7 @@
         <v>1</v>
       </c>
       <c r="F224" s="13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11672,7 +11672,7 @@
         <v>387</v>
       </c>
       <c r="F227" s="13" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11712,7 +11712,7 @@
         <v>1</v>
       </c>
       <c r="F229" s="13" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11732,7 +11732,7 @@
         <v>58</v>
       </c>
       <c r="F230" s="13" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -11752,7 +11752,7 @@
         <v>5</v>
       </c>
       <c r="F231" s="13" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -12309,10 +12309,10 @@
         <v>546</v>
       </c>
       <c r="E259" s="13" t="s">
+        <v>763</v>
+      </c>
+      <c r="F259" s="13" t="s">
         <v>764</v>
-      </c>
-      <c r="F259" s="13" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="260" spans="1:6" ht="26.65" x14ac:dyDescent="0.45">
@@ -12403,22 +12403,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="8" customFormat="1" ht="26.65" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>770</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>1510</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>777</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>771</v>
-      </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>1511</v>
       </c>
-      <c r="E1" s="16" t="s">
-        <v>1512</v>
-      </c>
       <c r="F1" s="17" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -12434,13 +12434,13 @@
         <v>air</v>
       </c>
       <c r="D2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12456,13 +12456,13 @@
         <v>aisle</v>
       </c>
       <c r="D3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12478,10 +12478,10 @@
         <v>aisle</v>
       </c>
       <c r="E4" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12497,10 +12497,10 @@
         <v>ash</v>
       </c>
       <c r="E5" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -12516,13 +12516,13 @@
         <v>ash</v>
       </c>
       <c r="D6" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E6" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12538,13 +12538,13 @@
         <v>ash</v>
       </c>
       <c r="D7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="E7" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -12560,13 +12560,13 @@
         <v>ash</v>
       </c>
       <c r="D8" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E8" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12582,13 +12582,13 @@
         <v>IKEA</v>
       </c>
       <c r="D9" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E9" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -12604,10 +12604,10 @@
         <v>IKEA</v>
       </c>
       <c r="E10" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -12623,13 +12623,13 @@
         <v>Otis</v>
       </c>
       <c r="D11" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E11" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -12648,10 +12648,10 @@
         <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12667,10 +12667,10 @@
         <v>dean</v>
       </c>
       <c r="E13" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
@@ -12689,10 +12689,10 @@
         <v>205</v>
       </c>
       <c r="E14" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -12708,13 +12708,13 @@
         <v>union</v>
       </c>
       <c r="D15" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E15" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -12730,13 +12730,13 @@
         <v>knife</v>
       </c>
       <c r="D16" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E16" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.45">
@@ -12752,13 +12752,13 @@
         <v>ties</v>
       </c>
       <c r="D17" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E17" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -12774,10 +12774,10 @@
         <v>home</v>
       </c>
       <c r="E18" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12793,13 +12793,13 @@
         <v>hip</v>
       </c>
       <c r="D19" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E19" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -12815,13 +12815,13 @@
         <v>toes</v>
       </c>
       <c r="D20" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="E20" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -12840,10 +12840,10 @@
         <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12859,10 +12859,10 @@
         <v>iodine</v>
       </c>
       <c r="E22" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12878,13 +12878,13 @@
         <v>entrance</v>
       </c>
       <c r="D23" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E23" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12900,13 +12900,13 @@
         <v>time</v>
       </c>
       <c r="D24" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E24" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12922,13 +12922,13 @@
         <v>oil</v>
       </c>
       <c r="D25" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E25" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12947,10 +12947,10 @@
         <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.45">
@@ -12966,13 +12966,13 @@
         <v>deli</v>
       </c>
       <c r="D27" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E27" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -12991,10 +12991,10 @@
         <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13010,10 +13010,10 @@
         <v>tai chi</v>
       </c>
       <c r="E29" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13029,10 +13029,10 @@
         <v>Maui</v>
       </c>
       <c r="E30" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.45">
@@ -13048,10 +13048,10 @@
         <v>dose</v>
       </c>
       <c r="E31" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13070,10 +13070,10 @@
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.45">
@@ -13089,10 +13089,10 @@
         <v>wine</v>
       </c>
       <c r="E33" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.45">
@@ -13111,10 +13111,10 @@
         <v>159</v>
       </c>
       <c r="E34" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13130,13 +13130,13 @@
         <v>entrance</v>
       </c>
       <c r="D35" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E35" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.45">
@@ -13152,13 +13152,13 @@
         <v>mow</v>
       </c>
       <c r="D36" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E36" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13177,10 +13177,10 @@
         <v>205</v>
       </c>
       <c r="E37" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13199,10 +13199,10 @@
         <v>330</v>
       </c>
       <c r="E38" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.45">
@@ -13218,13 +13218,13 @@
         <v>hall</v>
       </c>
       <c r="D39" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E39" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -13240,13 +13240,13 @@
         <v>shoe</v>
       </c>
       <c r="D40" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E40" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.45">
@@ -13262,13 +13262,13 @@
         <v>shoe</v>
       </c>
       <c r="D41" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E41" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13284,13 +13284,13 @@
         <v>wavy mane</v>
       </c>
       <c r="D42" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E42" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13309,10 +13309,10 @@
         <v>25</v>
       </c>
       <c r="E43" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13328,13 +13328,13 @@
         <v>wavy mane</v>
       </c>
       <c r="D44" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E44" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.45">
@@ -13350,10 +13350,10 @@
         <v>wavy mane</v>
       </c>
       <c r="E45" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13369,13 +13369,13 @@
         <v>wavy mane</v>
       </c>
       <c r="D46" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="E46" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.45">
@@ -13391,10 +13391,10 @@
         <v>wavy mane</v>
       </c>
       <c r="E47" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13410,13 +13410,13 @@
         <v>wavy mane</v>
       </c>
       <c r="D48" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E48" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13432,13 +13432,13 @@
         <v>twine</v>
       </c>
       <c r="D49" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E49" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13457,10 +13457,10 @@
         <v>249</v>
       </c>
       <c r="E50" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13476,13 +13476,13 @@
         <v>twine</v>
       </c>
       <c r="D51" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E51" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13501,10 +13501,10 @@
         <v>25</v>
       </c>
       <c r="E52" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13523,10 +13523,10 @@
         <v>189</v>
       </c>
       <c r="E53" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.45">
@@ -13542,13 +13542,13 @@
         <v>ammo</v>
       </c>
       <c r="D54" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E54" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13564,13 +13564,13 @@
         <v>hitch</v>
       </c>
       <c r="D55" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E55" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -13589,10 +13589,10 @@
         <v>116</v>
       </c>
       <c r="E56" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13611,10 +13611,10 @@
         <v>296</v>
       </c>
       <c r="E57" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -13630,13 +13630,13 @@
         <v>ATM</v>
       </c>
       <c r="D58" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E58" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13652,13 +13652,13 @@
         <v>ATM</v>
       </c>
       <c r="D59" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E59" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13674,10 +13674,10 @@
         <v>ATM</v>
       </c>
       <c r="E60" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13693,10 +13693,10 @@
         <v>ATM</v>
       </c>
       <c r="E61" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13712,10 +13712,10 @@
         <v>ATM</v>
       </c>
       <c r="E62" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13731,13 +13731,13 @@
         <v>tile</v>
       </c>
       <c r="D63" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E63" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13753,10 +13753,10 @@
         <v>entrance</v>
       </c>
       <c r="E64" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -13775,10 +13775,10 @@
         <v>15</v>
       </c>
       <c r="E65" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.45">
@@ -13797,10 +13797,10 @@
         <v>381</v>
       </c>
       <c r="E66" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -13816,13 +13816,13 @@
         <v>rye</v>
       </c>
       <c r="D67" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E67" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -13838,13 +13838,13 @@
         <v>rye</v>
       </c>
       <c r="D68" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E68" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.45">
@@ -13860,10 +13860,10 @@
         <v>wheel</v>
       </c>
       <c r="E69" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.45">
@@ -13879,13 +13879,13 @@
         <v>wheel</v>
       </c>
       <c r="D70" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E70" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.45">
@@ -13901,13 +13901,13 @@
         <v>echo</v>
       </c>
       <c r="D71" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E71" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -13926,10 +13926,10 @@
         <v>178</v>
       </c>
       <c r="E72" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13945,10 +13945,10 @@
         <v>dice</v>
       </c>
       <c r="E73" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13964,13 +13964,13 @@
         <v>ton</v>
       </c>
       <c r="D74" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E74" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -13986,13 +13986,13 @@
         <v>Noah's ark</v>
       </c>
       <c r="D75" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E75" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.45">
@@ -14011,10 +14011,10 @@
         <v>349</v>
       </c>
       <c r="E76" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14030,13 +14030,13 @@
         <v>hootch</v>
       </c>
       <c r="D77" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E77" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14052,13 +14052,13 @@
         <v>hootch</v>
       </c>
       <c r="D78" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E78" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14077,10 +14077,10 @@
         <v>15</v>
       </c>
       <c r="E79" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14099,10 +14099,10 @@
         <v>215</v>
       </c>
       <c r="E80" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14118,13 +14118,13 @@
         <v>whale</v>
       </c>
       <c r="D81" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E81" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -14140,13 +14140,13 @@
         <v>chihuahua</v>
       </c>
       <c r="D82" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E82" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14159,16 +14159,16 @@
       </c>
       <c r="C83" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[Book Chapter]],'NT Chapters'!A:A,'NT Chapters'!E:E)</f>
-        <v>Noah</v>
+        <v>knee</v>
       </c>
       <c r="D83" t="s">
         <v>251</v>
       </c>
       <c r="E83" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14181,16 +14181,16 @@
       </c>
       <c r="C84" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[Book Chapter]],'NT Chapters'!A:A,'NT Chapters'!E:E)</f>
-        <v>Noah</v>
+        <v>knee</v>
       </c>
       <c r="D84" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E84" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14203,16 +14203,16 @@
       </c>
       <c r="C85" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[Book Chapter]],'NT Chapters'!A:A,'NT Chapters'!E:E)</f>
-        <v>Noah</v>
+        <v>knee</v>
       </c>
       <c r="D85" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E85" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14225,16 +14225,16 @@
       </c>
       <c r="C86" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[Book Chapter]],'NT Chapters'!A:A,'NT Chapters'!E:E)</f>
-        <v>Noah</v>
+        <v>knee</v>
       </c>
       <c r="D86" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E86" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14247,13 +14247,13 @@
       </c>
       <c r="C87" t="str">
         <f>_xlfn.XLOOKUP(Table4[[#This Row],[Book Chapter]],'NT Chapters'!A:A,'NT Chapters'!E:E)</f>
-        <v>Noah</v>
+        <v>knee</v>
       </c>
       <c r="E87" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14269,13 +14269,13 @@
         <v>oar</v>
       </c>
       <c r="D88" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E88" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14291,13 +14291,13 @@
         <v>oar</v>
       </c>
       <c r="D89" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E89" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.45">
@@ -14316,10 +14316,10 @@
         <v>153</v>
       </c>
       <c r="E90" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.45">
@@ -14335,13 +14335,13 @@
         <v>oar</v>
       </c>
       <c r="D91" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E91" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14360,10 +14360,10 @@
         <v>414</v>
       </c>
       <c r="E92" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14382,10 +14382,10 @@
         <v>173</v>
       </c>
       <c r="E93" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14401,10 +14401,10 @@
         <v>aioli</v>
       </c>
       <c r="E94" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.45">
@@ -14420,10 +14420,10 @@
         <v>wine</v>
       </c>
       <c r="E95" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14439,10 +14439,10 @@
         <v>wine</v>
       </c>
       <c r="E96" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.45">
@@ -14458,13 +14458,13 @@
         <v>yam</v>
       </c>
       <c r="D97" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E97" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14483,10 +14483,10 @@
         <v>249</v>
       </c>
       <c r="E98" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14505,10 +14505,10 @@
         <v>463</v>
       </c>
       <c r="E99" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14524,13 +14524,13 @@
         <v>ash</v>
       </c>
       <c r="D100" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E100" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14546,13 +14546,13 @@
         <v>ma</v>
       </c>
       <c r="D101" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E101" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.45">
@@ -14568,13 +14568,13 @@
         <v>Noah</v>
       </c>
       <c r="D102" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E102" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14590,13 +14590,13 @@
         <v>hair</v>
       </c>
       <c r="D103" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E103" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.45">
@@ -14612,13 +14612,13 @@
         <v>bow</v>
       </c>
       <c r="D104" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E104" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14634,13 +14634,13 @@
         <v>ties</v>
       </c>
       <c r="D105" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E105" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14659,10 +14659,10 @@
         <v>178</v>
       </c>
       <c r="E106" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="57" x14ac:dyDescent="0.45">
@@ -14678,10 +14678,10 @@
         <v>Houdini</v>
       </c>
       <c r="E107" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.45">
@@ -14700,10 +14700,10 @@
         <v>325</v>
       </c>
       <c r="E108" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14719,13 +14719,13 @@
         <v>dummy</v>
       </c>
       <c r="D109" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E109" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14741,10 +14741,10 @@
         <v>entrance</v>
       </c>
       <c r="E110" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14760,10 +14760,10 @@
         <v>entrance</v>
       </c>
       <c r="E111" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.45">
@@ -14782,10 +14782,10 @@
         <v>208</v>
       </c>
       <c r="E112" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14801,10 +14801,10 @@
         <v>knee</v>
       </c>
       <c r="E113" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14820,13 +14820,13 @@
         <v>hear</v>
       </c>
       <c r="D114" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E114" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14845,10 +14845,10 @@
         <v>159</v>
       </c>
       <c r="E115" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14864,10 +14864,10 @@
         <v>entrance</v>
       </c>
       <c r="E116" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14883,13 +14883,13 @@
         <v>hen</v>
       </c>
       <c r="D117" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E117" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14905,10 +14905,10 @@
         <v>hymn</v>
       </c>
       <c r="E118" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14924,10 +14924,10 @@
         <v>ma</v>
       </c>
       <c r="E119" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -14946,10 +14946,10 @@
         <v>116</v>
       </c>
       <c r="E120" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14965,10 +14965,10 @@
         <v>ray</v>
       </c>
       <c r="E121" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -14987,10 +14987,10 @@
         <v>64</v>
       </c>
       <c r="E122" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.45">
@@ -15006,13 +15006,13 @@
         <v>halo</v>
       </c>
       <c r="D123" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E123" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.45">
@@ -15028,13 +15028,13 @@
         <v>entrance</v>
       </c>
       <c r="D124" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E124" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.45">
@@ -15050,13 +15050,13 @@
         <v>entrance</v>
       </c>
       <c r="D125" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E125" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
@@ -15072,13 +15072,13 @@
         <v>Noah</v>
       </c>
       <c r="D126" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E126" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.45">
@@ -15094,13 +15094,13 @@
         <v>Noah</v>
       </c>
       <c r="D127" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E127" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -15116,10 +15116,10 @@
         <v>ray</v>
       </c>
       <c r="E128" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -15135,10 +15135,10 @@
         <v>ray</v>
       </c>
       <c r="E129" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -15154,13 +15154,13 @@
         <v>ray</v>
       </c>
       <c r="D130" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E130" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -15176,10 +15176,10 @@
         <v>whale</v>
       </c>
       <c r="E131" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -15195,13 +15195,13 @@
         <v>whale</v>
       </c>
       <c r="D132" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E132" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -15217,13 +15217,13 @@
         <v>whale</v>
       </c>
       <c r="D133" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E133" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
@@ -15242,10 +15242,10 @@
         <v>120</v>
       </c>
       <c r="E134" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.45">
@@ -15286,1012 +15286,1012 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>1010</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>778</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>1011</v>
-      </c>
       <c r="D1" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>1086</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C2" t="s">
         <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D3" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C4" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D4" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C5" t="s">
         <v>379</v>
       </c>
       <c r="D5" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C6" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D6" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D7" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C8" t="s">
         <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D9" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D10" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D11" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D12" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D13" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D14" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D15" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D16" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D17" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="57" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D18" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D19" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="57" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D20" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C21" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D21" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C22" t="s">
         <v>330</v>
       </c>
       <c r="D22" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C23" t="s">
         <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C24" t="s">
         <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C25" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D25" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C26" t="s">
         <v>139</v>
       </c>
       <c r="D26" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C27" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D27" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C28" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D28" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D29" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D30" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D31" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D32" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D33" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D34" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D35" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="36" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D36" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D37" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D38" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D39" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="40" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C40" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D40" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C41" t="s">
         <v>236</v>
       </c>
       <c r="D41" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="57" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C42" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D42" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C43" t="s">
         <v>173</v>
       </c>
       <c r="D43" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C44" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D44" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D45" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D46" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="47" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="48" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C48" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D48" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="49" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C49" t="s">
         <v>165</v>
       </c>
       <c r="D49" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C50" t="s">
         <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="51" spans="2:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D51" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="52" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D52" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="53" spans="2:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D53" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="54" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C54" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D54" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="55" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C55" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D55" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C56" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D56" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C57" t="s">
         <v>139</v>
       </c>
       <c r="D57" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C58" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D58" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C59" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="D59" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="60" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C60" t="s">
         <v>280</v>
       </c>
       <c r="D60" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C61" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D61" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C62" t="s">
         <v>191</v>
       </c>
       <c r="D62" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C63" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D63" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C64" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="D64" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D65" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D66" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="67" spans="2:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D67" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="68" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C68" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D68" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="69" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C69" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="D69" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="70" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C70" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D70" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="71" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C71" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D71" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="72" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C72" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D72" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="73" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C73" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D73" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="74" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C74" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D74" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C75" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="D75" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="76" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C76" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D76" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="77" spans="2:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D77" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C78" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="D78" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="79" spans="2:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C79" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D79" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
   </sheetData>
